--- a/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_AIRLINE_TEMPLATE_AND_MODEL_PARITY_MATRIX.xlsx
+++ b/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_AIRLINE_TEMPLATE_AND_MODEL_PARITY_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parity Matrix" sheetId="1" r:id="R82c7bcc53e494081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parity Matrix" sheetId="1" r:id="R37068c908fd44e2a"/>
   </x:sheets>
 </x:workbook>
 </file>
